--- a/data/hdu_rank_all.xlsx
+++ b/data/hdu_rank_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\橙冰\信息学\集训队\2026 集训队排名\program\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\bupt_icpc_rankings\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF26E0B-D8E8-49C5-B2C0-85E6BEA0C950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A227C2E7-F0F1-40C7-9A3F-AF09B2C11DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12510" yWindow="0" windowWidth="12780" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HDU Rank" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="567">
   <si>
     <t>队伍编号</t>
   </si>
@@ -1715,6 +1715,14 @@
   </si>
   <si>
     <t>张鲁豫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>team0023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘林果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2062,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6081,6 +6089,74 @@
         <v>114</v>
       </c>
     </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>565</v>
+      </c>
+      <c r="B60" t="s">
+        <v>566</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>1323</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60">
+        <v>817</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>926</v>
+      </c>
+      <c r="I60">
+        <v>3</v>
+      </c>
+      <c r="J60">
+        <v>718</v>
+      </c>
+      <c r="K60">
+        <v>4</v>
+      </c>
+      <c r="L60">
+        <v>598</v>
+      </c>
+      <c r="M60">
+        <v>3</v>
+      </c>
+      <c r="N60">
+        <v>653</v>
+      </c>
+      <c r="O60">
+        <v>4</v>
+      </c>
+      <c r="P60">
+        <v>388</v>
+      </c>
+      <c r="Q60">
+        <v>3</v>
+      </c>
+      <c r="R60">
+        <v>331</v>
+      </c>
+      <c r="S60">
+        <v>3</v>
+      </c>
+      <c r="T60">
+        <v>476</v>
+      </c>
+      <c r="U60">
+        <v>2</v>
+      </c>
+      <c r="V60">
+        <v>559</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
